--- a/data/products.xlsx
+++ b/data/products.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1664,6 +1664,102 @@
       </c>
       <c r="F46" t="inlineStr"/>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Smart Video Intercom</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Video intercom with card reader, two-way audio, and call button.</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D47" t="n">
+        <v>5</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAYEBQYFBAYGBQYHBwYIChAKCgkJChQODwwQFxQYGBcUFhYaHSUfGhsjHBYWICwgIyYnKSopGR8tMC0oMCUoKSj/2wBDAQcHBwoIChMKChMoGhYaKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCj/wAARCADDAV4DASIAAhEBAxEB/8QAHAABAAICAwEAAAAAAAAAAAAAAAECAwYEBQcI/8QAShAAAgIBAgMEBQgFCQUJAAAAAAECESEDMQRBUQUSImEGB3FzshMyNYGRobHBIzdTdNEUFTNDUnKi4fAXJCWz8SY0NkJEVGSTlP/EABUBAQEAAAAAAAAAAAAAAAAAAAAB/8QAFBEBAAAAAAAAAAAAAAAAAAAAAP/aAAwDAQACEQMRAD8A+qQAAAAAAAAAANd9OvojS9+vhkbEa76dfRGj79fDIDQ9k2lh8y9Km2iqum+hEblu/q5AGrj4cPkQ/PbcvWFiw4ru7+QGHU2W654MUk9mZpvxNNY5GOrePvA48oU8vDKzjhJK2ZZLe3kxaiSaaYGGVpLa+Rgd26+pHIkvEpbJbZMM4SbjSu3noBieH1pUVUV8mqflkzOKUkl83quZjnTaXMDBKNeK7zyKakVz2WTO7ir7u9lJbNulWAMGo224xTys8jE8rfD6GWVqXdrMirilyv8AICj8UajTa38ikV4pc1yZaSqKpc8/YQ14HWXjCQEN1F03aysFLabjd0smTFV/0Mcd98XV9QIUV3VW1bGOS7sUo9Wy9d6Ku10K6i2TV9QItpUunQJp7WRK6cVTwWcKg2vuA+mwAAAAAAAAAAAAAAAAAAAAAAADXvTj6J0ffr4ZGwmuenUnHsjRa/br4ZAaQ14O7St59gqorb2FbTabLXywgJUX3V7TFKV2ktqMizF5ZjeHhYAiSXTfqYJu3zMrdmOappcgMS2yY55iuaLyttW+dmFupJZoCHy+xFZLxW88lRErpYKajcnu3ncCuItbN5MLrOMl5JRbSq3dFJ4fhWUBGo5N5wvxMckqba2JbwnKkjG/E8um+XkBWlfLvdTG8NyePr3yTOu8458iuLaWHeWwIVd6VrHKw8ReCjeXVb4bEnUrt45AFuyHSbv78h+GE8+J5ZReGrw39YCnWdkqMcpPqrukWTbXiXK/YRO1KOEllVzQEJ202tkRlxV7OsFXdUlncKUpU1tuB9PAAAAAAAAAAAAAAAAAAAAAAAAGt+nn0Roe/XwyNkNb9PfofR9/H4ZAaLHCRa+bTrqUzXmWbdUgCdyVbEST7yeaJTpJ5tmKUt2l9YDUvw0V1Lf8RKSp8+RjcvClVexgU1F4nmjE0m29vzM8q7uc8/acdN4b+wCKpV1MMr5+b2M2o7bxhcjHNWsJr2gYZZdqknlmGcXlLd5tmaSUVW7ox6itJVnmBx5J99bb8iJXunhujJPFqOMcyn9pSl7AMb8M5ZdJblZVVv2lprwS5XsmUi1VP5wFNt3kTit9r6lku7J82Q2km3eFf1gVVON4av7f8isou02yfF4Etniwmk76boDG08YtLPWit7vd26LT8VXs+RTNUqr/ACAhK3d/Oz1KScu46lttjbcyJ03JdaKTd6bqTV8wPp4AAAAAAAAAAAAAAAAAAAAAAAA1v08+h9H36+GRshrnp59EaNuv06+GQGhLLdBU3TeeZL8vrKuVJYVgL2VYujG/nNeWC6ik7bwY5JJ78wIk8+F59mDG03Ju8J0Wd5yUk8pLMdwEu73n0KNVfJWZI4pUupjeW76K8gQ4Wmmr6kTj0VnUemfaXEdl+jvEcTwU4w1lOEVJq6tpM84fpt249+MX/wBcQPWJQarO7Mc4eKrs8nn6aduP/wBYq93E6r0g9P8At/gezpa2hxkFq96MU3pRe4HtL01nD+so9JReFt1PnB+tb0sb/wC/aP8A+eJ3noL6wPSLtn0s7P7P4/i4T4biJuE1HSUX81vDXsA9wcbdypJZ8zjurebWLo6rt2Wtw6g46s+53W5NvJ1OjxupLUX6VyW+5BtG7l3fNFNoutzicJrOUd9/M5Dfdhuqaqyi2cJ89yt2sc3uQ3mm8FXO+r5gHFRtu6lyorN0lyS3+wU3KrstNpRja8Kx9YFVUE1WWVrvd3akWdvvN1nBRrvXja6inuwPp4AAAAAAAAAAAAAAAAAAAAAAAA1z08r+Z9G/28fhkbGa16ffQ+hmv94j8MgNCbdPvYLSajpuk72K2tuYVu/zAh7bIxzadtJukXbaT6FF52rWGBFOSeKoxyTTeMvzM3ll9WyksJ458wKarabrbYo3cEq26F20mrzbI71NW6SA1X1kR7vojxN7/K6T/wASPHXOj2T1ntL0N4pr9rpfGeJ9+2kBllOzXvTLUS4Hh4KVuepbXSkbBLTf8q+RTvNWzofTfg4w0tCWnKT7icmn0bSA042z1VfrB7F96/gka/qaHDLsrR14a8nxctWUZ6PdxGKWHZ3/AKq/1g9i+9fwSIPpLtlJ9ncTz/Qz/Bnl/o/xUpaelCUnhKj1HtjHZvE+5n8LPIvR550n5ID0bg6emmleDl21G5bJ77nE7O8WlG9zn1aqk65sCkajd74dbkxw3Hfy6ktVfNp0Q9u9zfRdCiINNP8AIidvb/oFUYpJ88kN1FX95BNq1HntvsVbTTbrbIiqlJ28vn+BXUVxa67gfTwAKAAAAAAAAAAAAAAAAAAAAAAa36e/Q+jf7dfDI2Q1r0/ddjaPv4/DIDQU3unjdBvryRWqwt28ewm8tUgIbS2VXtkrOsNc2TLMltfJEQzPIDas5MWo8/iZZPNt5Mcmnae3kBEm6vdrJjUbbddDI1dusPmElG0k76Aan60ml6E8Y1+10vjPDVOnZ7l618eg3G1+00fjR4J331A5z4ru8Z8sli7o6P0v7T0tWb0NJybcUnapRW/2nLlM1Xteff7R1n0dfcBhlqJ8LDTz3lJs2X1V/rB7E98/gkaobX6q/wBYPYnvn8EiD6U7Z+juJ9zP4WeP+j++l7Eew9tfR3E+5n8LPHuwVb0vYgPSOzWvkEc1OV2r7tOzg9m5040ss7DMXay0uQEN4Vrnsirpzab2WS0m7cVsRXdk2/JNlGPdt7fwIUpOb2ay76WZL70XuY50oru0vzIF4proRNJu2mTJtQV222iJLvPyQH08ACgAAAAAAAAAAAAAAAAAAAAAGs+sD6G0fPiI/DI2Y1j1guuxdF//ACI/DIDz9uneL5EybS2VvqUu6WNyZO08YAl7720uZDxvsFLxc8EN7gQ8rJS0kvPfGxaVpZ3Kya7tc63AiVY6ciXSfdqq+4j8OpW3K3bfRsDU/W1L/sHxzWy1NJf40fP7nZ7763XXoB2hlY1NH/mI+ee+BzeEguI4vS0ZScVOVOSV0tzpZ6HZnEaPaOtpa/GfK6cPlIfKacUr7yVOm978jsuD4qHD8Xp62pfycG2+7l1TR03e4Lh+C4qPD8Vq62prQjBRlodxKpKV33n0A6w2v1V/rC7E98/gkaobX6q/1g9ie+fwyIPpXtn6N4n3M/hZ4/2B/VexHsHbV/zdxPuZ/Czx/sD+qvoij0Xs11oxdroc1T7yauud/mcHs7OksHNjXd+rm9yC0lct8JESwqV/YUnK9nhp0WbyuS29pQclFO8tb+0qqduW3n0Emnd3WwTU7tf5IgXattVSMbdqVN71lmRu4JL/AMxgpu28K+QH1IACgAAAAAAAAAAAAAAAAAAAAAGr+sP6F0f3iPwyNoNW9YrrsPR8+Ij8MgPPI7t89iyvCeOpXvYdJEqeUA2k8vPMWr9hEpNvBCl92QJeyW2CrWU+obzfIqmmm+vUCrbTCbbT2RKpOvrsrdb880BqPrfv/Z72i62no/8AMR84vUX9pfafXvGVPhnGUU4trDVnU6nZ/Bav9JwfCz/vaMX+QHynxOqloalNbdTqEfV3a/Zfo7wnBz4jtDsvs5aSw74eGXyWxxtL0S9D+P4TR4jQ7L7G1oat40Um4vo0tmQfLTXkbV6q/wBYPYnvn8Mj3XV9XHolqb9jaMf7k5x/Mt2Z6v8A0b7J7S0O0OA4GWlxWg+9py+WnJJ1WzfmB3/bX0bxPuZ/Czx3sL+q9iPYu2/o7ifcz+FnjvYSTWlfRYA9D7Ov5GvLJ2EIJK843Z1/ZsahHDqkdmsUunIDFKG6y5NYREU6i3kyN1crKU0t7oAla7rxG8kRTkreIyz9Qyu822/yDapNLyANeGtr+8wvMW2m23hF5V3adJlad3ebA+ogAUAAAAAAAAAAAAAAAAAAAAAA1b1jfQej+8L4ZG0mqesj6D0P3mPwyA86+UzbTSWCYybaW1GNNcuZDbAyd6pFbbks77lFaTssp13cewCW6dLIjlNVXnZVXzfhe5PepdLAsqul9rZSDd4WKwVsRtOsJUBOvL9BL2r8Tid45Ou70pro0vvOIgNL9a0dR9jcHOPe+RjrtTcXVNxaj95qnq5cdP0khDipSWrJyehHKbknl+yr8j1njOG0ON4XV4bi9KOtoake7OE1aaOq7E9F+yexeJ1OI4DhnHXmu69TU1HOSj0TeyA760JfNZUSYHF7a+juJ9zP4WeP9gb6XsR7B239H8T7mf4M8b7BdPS9i3IPRuAf6FU8UdjDbJ1vZ1fJRbyn/A56q8Z6FEykt/8AXtD6dd/sK8qRNXhOqZBV1JJvMd/ZREX4VaaW/wBYkk491LG2xEl4kt+aQFW055TrCRV8984Ji3inTdJBNR6tvn5AfUQAKAAAAAAAAAAAAAAAAAAAAAAan6ynXYWh+8x+GRthqfrKV9haH7zH4JgeatW7SYmmsXXNhvmnT6Ir3r3rKoCY3eXz+4tKdvmzFdbZe2Bs8t/xAyd51yd9FsRLDWSHKmstJZZCl4lJ3b5dALXhdUUjV9ckK8N2mxF4aVq0BbWaejL2r8Tio5Orf8mlnFr8TiAWJMbi7tSks3v5FVCeP0kmsbpZAzEPYiFqCUn3pLd1VhvAHH7cf/D+J9zP8GeN9hZlpc8I9j7b+j+J9zP8GeN9hYlpN9EQei9n/wBHF1skqOwy5JbRdHX9nJ/IxvLs568NAEk8JewReLpqty1pxxlFI2/C8J7gS/Bbm9uRVu+8nu/tJk/HhrkQnnFY3QFd1W2PtI71u6RWblJNrw8rJjSw0+7de0o+owAAAAAAAAAAAAAAAAAAAAAAADUvWY67B0M78TFf4Jm2moes+v5g4fvN1/Ko/BMDzW846Fa6VtSEZJOltyRDksdEwLd5JVVvoiGrcm395W+83S3srltreN7gXlJ4X2iTp1v5kNpN4shYIJbwqWeoi7ilVX9pCy3REX5ZKMms74eT53+ZxEZ5OPdknaTrPQxOMUv6SP1pr8gIsCl/bhX94nuPkr9gEWGHFrdP7Cs33U23SXUDB25JLs/iL/Yz/BnjfYbuekvJG5esjjOLerw2jwM38lPSktTuq3v15Ys1HsnhtaGtHwSTXkQeh9l50445HYY5cqOt7Ni1pQUruSo7JvKS33fsAqnUXSz+I+bFKq5kyqKSwvqKJ3hbd7HmAeEqulmiIOrbyyablc1isGOTdYSX5FFqjSMUU3O2nS2XQtbaurpYvBF5f3gfUoAAAAAAAAAAAAAAAAAAAAAAABqHrQaXYHD97/3Ufgmbead60nXo/wAP+9R+CYHmMmlJOOL6lNOVRu1joFV45kK4pdd8AW76S3pMlt8sIo7aWzZPeTTe17gXu0+oTcrzgxp8+mwjKoOt76kFpSae9eRRSajhK3t5E4lJKW+5VtJ+e5RaeX5LkYm226qvMtJVJt1VcjHLNpfUQRNtyXQwSVz/ANZMkfmq6X3kSaTbi13gMKx8xyXJ52I1XqKr1Z03s5YLLw876FJZ5XJ/cBw9XhlKcpTqTxlmL+S6cZJqKveznS+a+b6JGPUdQf8ArIDRjlYWGZJvwprqtymlJ2lRavC2nldSit5TzgiOE8eYlhUskK2qeFzrcgNWVj5XX5lXK1awlzYbvZN29uhQdpU8N7+SKwXdSy8Eq2rlV7FW2o3fLAH1MAAAAAAAAAAAAAAAAAAAAAAAAab61P8Aw9w/71D4ZAAeVxb8Od0mXWyAAq+RPOQAETefroRdQbW4BBDw4VzEXdtgFES+cvZZim8IAgxr56+sSxGTW6dAAYnsnzz+JCxFgFFZu39X8DFu1fS/vAARSUm1vgtpq9N3yVgAUfzJFZ/M+oAgj+pT5spvh7Z/EAoLKbfKyJruxVYpsAD6lAAAAAAAAAAAAAf/2Q==</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Smart Water Tank Level Sensor</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Wi-Fi liquid level monitor with mobile app, depth reading, and alerts.</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>450</v>
+      </c>
+      <c r="D48" t="n">
+        <v>5</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAYEBQYFBAYGBQYHBwYIChAKCgkJChQODwwQFxQYGBcUFhYaHSUfGhsjHBYWICwgIyYnKSopGR8tMC0oMCUoKSj/2wBDAQcHBwoIChMKChMoGhYaKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCj/wAARCADDAV4DASIAAhEBAxEB/8QAHAABAAEFAQEAAAAAAAAAAAAAAAQDBQYHCAIB/8QAWRAAAQMCAwMFCAsJDAoDAAAAAAECAwQRBQYhBxIxCBNBUWEUInGBkZSz0RUXMjdVVnR2laGxIyRFUldmkrLSFjM0OEJiZXJztMHCGCZDRFN1oqPw8YKT4f/EABoBAQADAQEBAAAAAAAAAAAAAAABAgMEBQb/xAAuEQEAAgIABAQGAgEFAAAAAAAAAQIDEQQSITEFFWFxEyMyQVGRFDMigbHR4fD/2gAMAwEAAhEDEQA/AOqQAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAELGZZ4cOkdSORs12ta5Wb9ruRFW3ToqiSCsc+FWVqNa1ESROZRd9eleOgE0ETmKvnJ17rTceipG3mk+5r13vqU+5q7uXc7ubz29fnOYTh1Wv9YE8EFKau7lVi1zee3785zCe56rX+sSU1c6OFGVzWuanfu5hF3/ABX0AnAirDVd0yP7qRIVbZsfNJ3q9d76lKOmrmwStfXNdK624/mETd69L6gTwQHU1ctMxja9qSo5VdJzCap1Wue3QVayQKlYiMYiJI3mk79elb30AmAhxQVbatZJKxHwXW0XMolurvr9B4jpq5sMzX1yOkdbcfzCJudel9QJ4IuFSVEuHU761u7UK3v03d3XwdBKAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAjYjzi0ruZmbC/eb37lsiJvJdPGl08ZJIWMrE2gctQ1zo99l0atlvvtt9diaAACgWmozHhFNiTqCoxCCKrba8b3btrpdNV0Lq1zXtRzVRWql0VF0U1rnOWaozDVQw0mCYtFFG1ZKO+7WNS11VF4r1pa+nQRss42zBu5qmjnlny7Uycy+OZbyUcv4q9n2p2no/wADmxRek9ddv/dvTff7S8ifEpxZpplj/Hff8evrH5mJ6feG1AfGrdLn08564AAAUACHhDmPw2ndHM+dit0kfxdr0kwjYZz3cMPdMbYpt3vmMSyIpJAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAYVtA2kYLkuWmpKptVX4vVJenw6hj52eTt3ehO1TNTR2x1keL5pzxmqujdNikmNvwyOS28sFPHuojW9Sa626iYjaJXD238e4pstzaqf2Seox3HOUtT4DXLRYzkvG6GrRqPWKd7GORq8FsvQpllXimEuq4K2rpMUbJO+ORVhnekbJEvdu7dLqltUROtbGJbRMn5c2i4suI4lRYvRVVLR3fPE9I+djSRqNRWq117I9y37FTW2ltI2tVVyrcIkhVsOXK9r7ot3TRqlrpfTwXKv+ljgnxaxL/74zHpdieSWsqJGR5yljimWFHMZEqPs5G7yd7w75OPQvhKr9iOTqCeilqafM1TA+Js8qNkYjW+6vG5dxFTVE100VeorpLZlNtlxqpgjnh2Y5rfDIxHse2NFRzVS6Lw4cCTQbbKOGvp6bN+W8dyuypcjIanEIPuCuXoV6e58ZVXEMOhkimXBsY5prmvYksrkSLca7cRrd6yJbTd8F+BcnYfhGN5aqsMraKqSjxRHwrDVrvOXdb7vj3tuKdN7KTyqzM76LJiGFY1muuxqoXBIsOxKhlbJhuIRO3O6ERdEV17Ou1EVHJw4F2nyjiksmO/cqdsOI0kcnNtfolWllWydCX3te0i8mnEqnEtkmGd2yrNJSSzUjZHcVZG9UbfxWTxGyarEaKkejKqrp4Hql0bJK1qqnXZVO6fEckaisRER27+n5n8xv9uO/h2LJub95/7j/adKeAxVMOC0UVciJVMhY2REW/fImupOLf7N4V8JUXnDPWPZvCvhKi84Z6zgtPNMy7aV5axWPsuALf7N4V8JUXnDPWPZvCvhKi84Z6yFkmuqWUVFPVSo5Y4WOkdupdbIl1sYazaThcqXjpaxU7WtT/EumacZw+TLuIxU9ZTzzSQPjZHFK1yuVWqicFNLwU80LUR7HJZNdD5/xnxPJwlq0wzG/u9vwvgMfE0tbL/o2rhGcqKmw+GF8VS/m22V9k1+synBcUhxei7ppmvazeVlnpZboaYpruisiLY2JkXEaKjwNIamqhhkSV6qkr0ZxXTjxObwfxfPxWf4WaY1r2T4j4fiwYufHE72zIFv9nMK+E6HzhnrHs5hXwnQ+cM9Z9S8NcAW/wBnMK+E6HzhnrHs5hXwnQ+cM9YFwBFpMQo6x7mUlXTzual1SKVrlRPEpKAAAAAAAAAAAAAAAAAAAAAAAAAAAAaI2FVqU8Oc2vYrr5jq1VUX+qb1lduRuda+6iqc/bDnJNSZvktZH5gqnW8O6prijcssszFejdENQypS7Hq5U1svFCrdeteviYrUzvoUSd8u4xHWu2PeVLk3CMZZiiblPWM51rUcrVhVLovSl1NLV12UpffdfbrfivlF1ve638J8S9kut16SXT07Xxo511VTOejTujby9a+U8SL3j/Av2H3EpI6NW2Rzlcl0QtE1dM5HW3WpZdES5atZtHRWbxXow7kr+9NB2V1V6RSyZiylgeceUtWUGZcPZX0kWW45mRve9qNek9kW7VReDl8pe+Sv700Py6q9Ip9of40+I/NZn94QwbLl7ROzb4rU/nE37Y9onZt8Vqfzib9s2YANZ+0Ts2+K1P5xN+2PaJ2bfFan84m/bNmADBcE2S5IwKeSbCcCjpZJG7j3MqJe+S97av6yTPg2UafEGUNTFDDUyN342TTvbzifzVV3fW6UTVDIMTqHtgk5uR0SN4ytZvLEvQrm9LV6f/FTB8YoZKuLm54fvORyvWJ9CmKUEi/jMalpI+nTRE+sxvw2HJPNekTPrENK5slI1W0xHuu82D5Pir4KLmoH1sy95TxzPfIqdLt1HXRqdKroMZ2c5QzDRR0+J4TFV0rH841qzSWRyIqX0d2qhj2EYT3Mjo6CmVlM9Lyw4bhS4VDJb/iyyKr1b2N18JnGDzOSBFV7HsSzUdE20SW0RkSdKJ+N/wCkivC4aTzVpET7Qm2fLaNWtMx7sO9onZt8Vqfzib9se0Ts2+K1P5xN+2bLbdWpdLL1H03ZNZ+0Ts2+K1P5xN+2PaJ2bfFan84m/bNmADQ2TMr4NlDlKVWG5coWUNE7LSTLEx7nIr1nRFW7lVeCJ5DfJqCH+NTUfNZv94NvgAAAAAAAAAAAAAAAAAAAAAAAAAAB8d7lbmgdhlnUucFRLIuYaq3/AEm/natWxoTYQxUos4IvFMxVSL/0muLuzy9myHsRyWe1HJ1KlzyyCGNUWOKNiom6m61EsnUUa2OVk0fc1Mku81+85b2aqJ3vBeldChSpUyVCR1GFLFFvqnOc6i2ToW3T5TebOfS6MllalmvcieEtc+0bDcGxF+F4jFVtfFZXTsaj26pfhe/SXVrEa1GtSyIlkQ05tDj/ANbq7wR/qIdPDYKZ7ct/ww4nNfDWLUbTlzXQ48xZcGiqaxIFRkiIxI1Te1v3yp1EndvHfdVLpey8U0MJ2SMRKTFP7SP9VTN5n6KjOriUy44xXnHXtC2HJOWkXt3linJX96aH5dVekU+Uj2x8qbEVe5rU/cszVVt/vCFDkoe9i75fUfrqQsXp4arlMV8VQ1HRrlhl0Xgv3dDgrXmtEO61piszDbdZmjBKKfmavFKWKT+e+yeXgfaHM+B16femLUMvR3szTHKbCaakp+Zo0WONNdy6qi+VSwT4TT1GKzU09DLK/d30eyma1rk6ldey+NEOuOGx/lxTxWWJ+ltlHIqIqLdF6T6ahq6ejy2jFbX4xhrUdzaLTo9Y1W1+C3avkKTs+11Okaw402pYrd5GVNBzUipfraq3X/4lP4lp+mdrfzqx9UabengbKqOu5kicHtWyp/51FolwVqzOlbDFzi8ZIJX0znL27nFTGaDaXRPpmPq4HsS2srdWu7etPIUMRzlX1DWzYPWUTYVs9Elp5dWdKqtv/wAKRw2TepjTSeMxa3E7ZWzBWuka6aBj3N4LUVElTbwI7Qu0FOka773Okktbed0J1InBENbVGPO9kOefmdI3steJicFXoWO1rf8AskN2itigcr1ZVtYtlqaeNWsTWyXve3hvxJnhb/bqrHHY/v0bJufHPa1LuVETtNc02dJMYru4qCppY6i+sSTbz91OK2RPUiF3mw1tZuvxOWWocnBqyKjG+JLX8dyJ4ea/VOl44mLx/hG18lzDg0M6wTYpQxzJxZJO1q+RVLhBPFURJJBIyWNeDmORyL40MIxHLeB17N2tw+nm0tdzEvbwlnpsnYFhsvO0DaqlW992GocxPIhf4FJjpM79lfj3j6oj9ocP8amo+azf7wbfNFZYfflNzIkssjUyyiXler1/f00uupvU5bRyzp01tzRsABCwAAAAAAAAAAAAAAAAAAAAAAAD4/3K+A0PsCTeoc4J+cNV9jTfK6oaI2D97TZyRqaJmOrS36Jpj7s8nZsznY0W1n3/AKinxZ4+p+v8xShW0FXU1PP0mJS0ybqN5tGI5vBddenX6kPKYZXpNE5cYmdG16Oex0ad8ifybpwNZlnEJze+aipwXrNP7QWXzbWrbijP1EN0bqGoc+svmutVOpn6qHf4fPzZ9v8AhweIR8uPdddlzbUmIp0LIz9VTNXs71dOhTE9mTPvbEf7Rn2KZpzauuiJ0KU4qfm2W4WPlVYLyU2OTZbvKmjq+ot4nqQcVdu8puttxXLLE/76Fz5K3vTQ/L6r0iloxpbcpqsX82o/Tnm4/rh6OTpSWxI3qpKifYt8TksV0lRDrs5KymVMFPW0z6esiZNA+12O1RbLdPr1PlTh+H1EkfdFHSyycGuexFcngXiU4pNSYx6JZVtdOkpO47NNRbvCAynw+Jj6amp4aZETvm80jU79FRFVF46oTJUc2GKFqrG1XXkRO95xUtdUt16/4niRZWrGlO+NjUd36Ky929SdR7Vyqqqjk167rp0lZjfWSI10Qa/DaKojdUOpKaqqlYkbJHNRVVOHFfdcE4qUaShkqnUs+JQxNkpWywIxGbrVRVsjkS6ot0RPAty6vezcRN1qolrXTqKEs/aWjfZE1jexsNNTPkfBDDG+T3bmMRFd4VTiUZqi3SR56jtLfUVC34l60mesqWvrskVFZZOJa6qtVb6lCpm7S2VUqr0nVjxuW+WVnyHKsvKWnVfi5b/vIdCHOWzZ29ykJ1/N1fStOjTzc8ayWh6eCd46yAAxbAAAAAAAAAAAAAAAAAAAAAAAACmkNgMbX0edd5Nf3SVf+U3eppPk/fwPOvzlq/8AKXorbs2LVPfSyR99CjZHoxm+q3c5ejTxlOnrkqZFbTy00tuhrlunC/2p5SfVU0NU1raiNJGtcj0Rb6KnBSlTYfS0r1dTQMjcrd1VS91S97eVS+5Z6VHKltENUZ3jvmar8DP1UNs7qGN49lOHFa91WlS+F7kRHIjEci20vxOzhMtcV92cvF4rZactVo2aM+9sQ0/2jPsUzhrN1j1XirV+wt2XMDiwWmkjjldK+R285zktw0REQuz/AHDvAv2GefJGTJNoX4fHOPHFbd2ueSt700Py+q9IpZcfW3KXrPm1H6cvXJX96eH5fVekUsOZXbvKVrF/NuP05y4vrh05folnTZLJxKjJLqWznbrxJEL9T0Zr0edFl2hf0lZZk6yAkm608OmMpr1aRbSfz3aeueVE4luZLqenzWQjkTzpMk/WpGlqO0iTT9pFlm7TSuNna6RNP2kGabiUpZu0hTT8TemNha73PL26ltnk7T7NL2kCeU6aUc97IuzBb8o2ZfzeX0rTpI5p2Uu3uUVMv5vO9K06WPD4mNZbe73OG64q+wADBuAAAAAAAAAAAAAAAAAAAAAAAAKaR2AORlDnZzuCZlq/8pu5TS3J2RFp863bvWzJWLbr0aWqrZstKyBeD1/RX1FCR9C5yuel3O19y7UxKTaLiTN5UylVLZ6t5tVk3+PVzdvrNjxy7zY1WklarmtVUVE726cF16DbJS2PXNHf2Y48lcm+WVsSkp923NJbx9R6Snjaio1tkXRbKupdZEaxzUSFXXW12omnhKnNM/Eb5DP4jXlWeOFkauWNu7vcT09O8d4FLtzTPxG+Qj18bG0zla1EW3QhMXOVqvkr+9PF8vqvSKY3nB27ykapfzcj9MZJyV/enh+X1XpFMVzy7d5R1Tb4ux+mJwf2Qpnn5dmVRvuvEnQOsmpaKd17XUmJLuoeraHlVsnSTdpS54hPmufGS9pXkTzrmyWyaqeJZu0iLMiIRpZ+0RQ59JE0/HUiS1FiJNOmupFknv0m9cbGbpcs+nEiyzEaSZLcSNLNfpNq0Y2uqzTEKWU8SydpDmk7TatWNrpWyJd7lDzL/QDvStOmzl/Yy7e5Qc3/ACB3pWnUB83xfTNb3fR8JO8NfYABzukAAAAAAAAAAAAAAAAAAAAAAAAU0xycv3rOnzkq/sabnU0zycktHnVF+MlX9jSY7IluVqKnFbn08x7tu8W6eG56ISC6dYLNS00csDJXxMc6S71VU1W63JiNq2tpebkbEP4K8h9xsaqOiRYnp/Kj0W3UVHtkbQSNlfv2VUa5eKp29pPLpG9w1jyV/emh+X1XpFMSz8tuUZU/N6P0ymW8ldFTZND8uqvSKYhtBW3KLqfm9H6ZTXhv7as+J/qsv0T91D06cgLNZOJSdOvWe5ybeHzpzp1PscuvEtiy3UqMlsnEnkRzrjJP2kWae/SRpJtOJFlm7S1ce0WyK8s3Ejvm46kSSbtKDputTaKsJulvlKEkpFfLfpKMkvaXirObq0suvEiSyHiSXtIskl+k2rRlay9bEXb3KAmX+gX+ladSnKuwzXb9L/yJ/pGnVR8pxsaz3931fBf0U9gAHK6gAAAAAAAAAAAAAAAAAAAAAAABTSuwyZmD5uz5liuekeKMxiXEGRO0WWCVE3Xt6001t1obqMI2g7NsHzlPTV00tXhuNUqWp8ToJOanjTqv0p2KTEolmMk+4iLzUrr9DW3sW7EsfpMNSNa2KsYkl0bu0z5L2/qotvGa39qvNKJZNqmZrdF0bwHtV5q/KpmX9FvrAziTOuErG7c7vV1lt94TJr+gVsPzDhL+56WOaZZF3Y23pZmoq8OKtsnjMB9qvNX5VMy/ot9YTZXmr8qmZf0W+sgbc3ULTmzFaLAcu1uJ4nMyCjpo1kke5baInBOtVXRE61Nde1Xmr8qmZf0W+s90uxaKtr6eozpmnHM0Q07kfHR1su7BvJ0uYnuiSYSOTRh1Th2yTDFrInRPq5ZqtjHcUZI9VbfxWXxmt9stVPgu3J+JzYZilTRy4JHA2SkpXSpv86q2umnQdMxsbHG1kbUaxqIiNRLIidSHotS80tFo+yL0i9ZrP3ckOzvCv4DzJ9Gv9Z4dnSJeGCZj+jX+s66sLHX5hl9HJ5fi9XIaZzj+BMx/Rr/Wev3axfAmY/o1/rOurCw8xzeiPL8Pq5DfnOJfwJmP6Nf6yg/N7VTTBMxfRzzsOwt4fKTHiOaPwifDsM/lxq7NSL+BMw/Rzym7M6r+BMw/Rzzs63hFvCW8zzen6V8swev7cXOzIq/gTMH0c8prmFy/gTMH0e87Vt4RYnzXP6fpHlWD1/biZ+PPXhgmP/R7ymuNP+Bcf+j3nbtvCLE+bZ/T9I8p4f1/blXk9RVlZtnqMRXDMRp6RuDviWSppnRIjucaqJddNf8AA6qAODLknLab27y9DHjjFWKV7QAAzXAAAAAAAAAAAAAAAAAAAAAAAAAAAsLAALAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAD//Z</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>9-in-1 Indoor Air Quality Monitor</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Environmental sensor for temperature, humidity, PM2.5, CO2, TVOC, HCHO, and light.</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>950</v>
+      </c>
+      <c r="D49" t="n">
+        <v>5</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAYEBQYFBAYGBQYHBwYIChAKCgkJChQODwwQFxQYGBcUFhYaHSUfGhsjHBYWICwgIyYnKSopGR8tMC0oMCUoKSj/2wBDAQcHBwoIChMKChMoGhYaKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCj/wAARCADDAV4DASIAAhEBAxEB/8QAHQABAAEFAQEBAAAAAAAAAAAAAAIBAwQFBgcICf/EAEgQAAEDAgQEAwQGCAMECwAAAAEAAgMEEQUSITEGE0FRImFxBxQygRUjkaGxsggzQlJydMHRJCVkNmKS8Cc0NUNEU4LC0uHx/8QAGQEBAQEBAQEAAAAAAAAAAAAAAAECAwQF/8QAJBEBAQACAgIBBQADAAAAAAAAAAECEQMxEiFBBBMiMlEzodH/2gAMAwEAAhEDEQA/APqlERAREQEREBERAQohQUREQaip4iwum4lpMAmqg3FquB9TDBlPiYw2JvsOunWx7FWuG+KcK4jz/RU75ckENSc0bmeCXNkOo65HadFx+L+z/F6/i6fiWPGWxV8dfTy0dMGgw+7xNyljzlzhzmyT/CbXeN7Kzwf7OMTwqJ1PX4s+ngFJSwNkwuofFKXQmYDMS3VrmyNNuhB6aorvqPGaOrYSJDC7nPgDKgctznNeW6A6kEg2PVY3EXEOH4BDA+vfM6Sok5UEFPC+aaZ9iSGMYCTYAk9gF5vXeyWpqpMUllnw188zZfdZJGOc6B7651QHA20OUgEjW/kukxjhDEocUw/GMCxSSrxGiqJpGw4xO+SJ0crMrmNc0XjtoRYHaxVm09OlwjH8LxfD6etoK2J8E5LWZjkdmBLS0tdZwcCCC0i9wQthFNFLLJHFLG+SMhr2tcCWE9CBsfVeR1HsmrKs4hVVlThk2J1cRkE3KcBBUuqzO4x6EtaBZoPxaXO63Xs34Bq+FeI8QxCsqoqlsrJI2SskdnlD5zLmkblAzC9r5nHexANld1NR02C8X4VjNTNFQ+/ZInPYaiWjligLmPyOAlcAwnMCLA9Ct0yrpnx8xlRA6PKH5hI0jKTa977aHVeSQ+y/EzR4hQVH0S+nq6v3h85qql7pGe+NnyGFw5Y8ILbj+pWYPZZIzEYHQVFDBh7sRnkq6aOMhstE6dtRHCBawLZGa9LPeBup7X09Gw3F6OvpopY5DEZXOa2OccuQlpcD4Tr+ySPLVZH0hRchk3vdNyX/AAv5rcrtbaG9jqbLymn9ksz8PxllZU0BrqrD3UlLUsiJdA4zzyOOtiGubK1psbkBwVp/slqK6SunxCLAYhUwVrYqCnicaaklmhhjY6MFo6xFziANXaDqns9PW5a6jje9slXTscz4g6VoLdba66a6eqk6opxLJE6ohEsbQ57C8BzQdiR0C8il9j76hk0lWcJnrJffi+Z8RcXGaBkcVyRc5HtLvK9xqsKb2NYrM/FRPiNHO6rheG1Mkj87nPbG0se0M1YMhsS4/s2aDdN01HrkuNYWyvoqJ1fTe9VokdTxh4PMDLZ7EaaXCtvxjDxiFDRMqWST1rJXwcvxtcIsufxDQWzBee4h7LKlmNT12DMwGIOnrXU8c1NdtMyeCJjXNaG2Lmvjc7LoDnOt7qfAfs2xfhzH6PEamqw90TJZ3SQRF3hbJBFHdlmNbfNFf4QLO7jWzKpqOvn4twOGHH5Za9jGYCcuIZmkGHwhw063B0te503WwpsQpKqCOWGpiLXwtnAc8NcGOALXFp1A1G64bGfZTDitdj9dU1YbPiFRNK2KO/KnYYWNibOLa8uRpeLd1zld7H8VqaWopTWYSMzZHe+5JPeZi+BsfIkNv1TbXGp0DdAblameTNxj0zFeJcJwvI6uq2xwOYX+8AZoRZ7WZS8XAdmeBbffsVshU05c9oqIS5gDnASNu0HYnXQHoeq8rx72STVtfjUlCcJp6Ko5jqOkdERHG4mmdYtAs0EwPuW/v9dVjYh7J8RrRWxl+CUzJX1EgkgZIJJhNIx3JlNv1cYaWtt2Zo2xWvLL+M+M/r1GDGKGaSqaKhjG07wx0kjg2NxLQbscTZw1AJGx0WWZ4eeYedFzgAeXnGax20vfovOcW9l0NbxDX1TYcKGFyifkUToPDGX0rIWnLbKLOaXad9NVz3DHC2I4X7RsIppaEVJoql9VUYo6kka8tNGI8nOcMr2B1g0A37tFiS8rL7h4z+vaSFRTsqWXXbDeIiLyPQIiICIiAiIgIiICIiAiIgIiICIiAhRCgoiIgKLiqlQcVYLFW2V9NM2nkEczmODH5c2V1tDbrquZfDxSympZGT07546UmWIlpEkxJs29hsLa6bea6lFrTLlXTcXkQBtLhrXOjLpCTcRuubNAzXdoBr5+StTzcaNlcY6bDXMaS1rRbxjSzjd2nU27m17arr1WyaHOMk4l5FQ2WGiMxgD4jGcrRLn1YSSSRltros2BuLO9zdUPia5rpROIwA1wsch1uRrbQFbVaWfB6ifH4a6bEJXUsMglZS6huYMLddbbknbrrsLBq6WTi+HI33elmZy8zjUyN5mewuLs0AvcjQ6b20V+nqOKIqiBs9JSy07ZCJnNcM7mW0LPFuddxpoNRcqy/hfE+VFHHxBUtY0gkHMbEOuC3xdAALHTrvZZuF4NiNLXRzVuNTVELLkQ3cGk20BJcbhv2nd1zqoqNa/iOGrqTRQsnDpTyxK9giEdvDYaOBv8RN/IHpYNTxc2sZAaehcxwzGbl2a0ZrG/j3DdQBvtor+EcP1lFiDKifF5qiIOfI6PLlzPeSTcg/CHEkN6XWFFw1i8HPZSYzHTxyAN+rifdxA1e7xfG47keWlwmhN0vGg5sgp8NJLgxkZ2y3dd4Obe2XQ/cRrcdPxfzWN91w9zAM5LXZQTa+TVxNv2b28/JY9Jwxi1JMyVuOSySOe0Su8TczMwLza5GYi4B6XFtrLsgU0OZe7ieaknE8MMUrahuT3N7czorG+r7je24HXyWEJOOGluelwt5uGEA2bv8V819fTa+lwL9qCpIOLe7i4PL2U9I4Fo8D8rQDYaaPNxcHW9wDoCdBvMNbWmkH0k2EVGY35Qs0jppc/j0W3IUS26suksYDmkKBus50asuj3sukyYuLFKAqb4yFCx7LbFjdIiLyvQIiICIiAiIgIiICIiAiIgIiICIiAhRCgoiKhQUJVslScVBaiKKtkS+thcnsFdoIl9bG4PmLIoCojiBuVS56ArSJNBcbBYDcTDK6akkopmSh+WLZ3ObluXjs2+lz1IWwhPicD2WhqqYvr6qqGH1hnZMGtnikAkyBg+HNoW3JGXa9yt8cxytmTlzZZYyXH+tlhVazEqbmCCSnnaBzIpGkFjv3SdiR5LKBuFh4C1zIpmllUwFwdlqG+IEtF7uuc2vUaDZZepJItYkqZ6mVk6a47bhLl2qqhRzW3BVQQdtVmuiV1MbK3dA6+wJHcBZVdSyiHd91IKCllFzVcVLK7NMdzFZdGs2wUCwLUySxfREXNoREQEREBERAREQEREBERAREQEREBCiFBRRcVUqDirBRUKKqqI2JsBudFbqp3U7mNjawsIOYl2rOzrdRv57K7fK5p6XsrNfRNqcrskeYfES3xEAGwDt22JvforNb9s5b1+KFDUvqcofynR5Bd40zvHxWadQAe+oKvkODi2+g2PUqzh9FySJJGMz2u0EZnMLtXjPubn0WQ43kdbYaK5a36TDfj+SNgNhqiqVRSNA0IPZaGY8RtllMclG+JziWty2c1tzYA7E2tvt5rcVsUk9JLFDM6CR7bNlaLlnmFyVXistBWSQVfEcbZYnFpjdRnUaFo0GpsdT+C1MvH4Zyw8vnTpMPfiRnlFbkEPLjDS2wOe3j26E6rOGmi5zAn4hXysqo8dp6ujY/LIyOlyh3UgOOvULo1N7WTU0qqEA+vcJdVRVY25nEOsQNfVa51ZVR1M0dTJA2Iy5oXxML7Ri2ZrhfR2+uwWziPiI7rX1GHSzSylxjbE51mthvG4NPxku6k9vILWFm75OfJMtTxZNBLNVQyPqGRs8Z5YaTcM0tmB2d3CyGm4HdY2GU81KyoFQYCHSuczlR5LMsAA7uQBa/or7dr/ADWMteV03hvxm+1wKqg0qSy2qqWVUQSREUBERAREQEREBERAREQEREBERAREQEKIUESVbdupOUCtRKoq3VLql1dIkdrWvfotPiWE1VVUvngxSrpjlDWtiOgFiCSDod/uWbWUjK+mMUxkaxxDvA7KdDcarnMZoRh8TWGTiGsLsz2z08ud0JsG6fiBrqSrMrjfTOWMzntuafDquOppnGulMUWclpJJfm6E3tYefbSy2gFhYLkMLw/6SErG1HEVCGODzznhviN9Gk3v3XS4ZRe4Ubaf3ioqA0k8yofnfr0v2Clyt7XHGY9Mq6orcsojIuCb9lbNQ7pC9NyLpkKjmMfbOxrvVoKxX1uTV7Q0f7xssWbHKOH9dWUUf8c7B+JUtXTahrWCzGho7AWQrmp+M8CgP12O4RH61cf/AMlaoOOOH8SrPdKDiDCqiqOohiqWFx+V9U2adSi1wqXO+GQH0Ko6WTKfG7bur5GmyJAFybW63Wlk4ec+sfUDEK5vMeXujbIQ113B1rdALW0/+lDB3DFMFMNeXTNe4h2Y6uAIIBI9FpKvDjSVj20+D4xMWvcI546u4IvfrsB0H/6rM7j0xlx45/s6rDMOloGT/wCJkn5jg6z+lhbfv/YLYtN2gjZczw3glMyRmIGHE6adr3WjqqguJFrXIBtbU6fNdKBlcbbO/FS25e6sxmM1EgbKYKgqgqNJoFQKSiqoiKAiIgIiICIiAiIgIiICIiAiIgIiICo7ZVUXmwQQcrZKk5RW4zQAk2G6q9jTZjpLOdew0BKqCWxvc1uZwFw29rnsuZqah0b6lz6l0NVA60FK4tc9weASA7c3JI0Phy+S3hhc76cuXknHPbpiC3f7VRRps3uwa+N0eXwgOfnJA2N/NSWHWXcFx3tc4nqOEeA8RxWhDPfRkhgLxdrXvdYOI62FzbyXYryr9Jc29llT/N0/5lKPnGp9oPFdUS6ox7EJCe87x9wIA+S1NVxNjM9+diVU/wDilcfxK05Jc5rW7k2CzG4VO8Sgvja6N72OBvfM0agaalZaWZsTrJL56h59bFYUtXOSS6V34LImoZWUjKgPYWOZnI1Dhra1rffssNkBlp55jJExsYvZzhmcewCC1JM917yP/wCIq1DI6OoZKxxD2HO13UEag3+SyJqVjMOZUiZpe51smnn87i33rBadT/C78Cg+oKavqJMKhmEj2vfC2Q2NtS0FdbwTxZNVU5pa6QvmZcB5Orh0v5rhqN9sApT/AKVn5ArHD0hjqHOBsQ66D1/hHGGuqZqKzs8Ia4noc19vsXc08oeAvJOFZMvFNYOhii/9y9QpjoCNlqI2YVAHSDw2De56qA8TQOjiAVZxCeV1RDR0jnNlec0j2tB5ceuuulyRYb9T0Vktuozll4zbLLHjs4fYUB6rCZNU0VVHDVu51NKcsc9rOa7o19tNehHzWc8Wd66pZYY5TJIKStgqYKzW0kRFAREQEREBERAREQEREBERAREQEREBQmNmj1U1aqTZjfVWCJ2UVS+iLcZSD2xgueQGgXJJ0HmsW2H85oE0DTGH3jD22Ob4i4fI/esbG6+ho4Gw4k9zIqrNDcA21GtyNtDuubfUcJyGeSoqXvZrJI+QyZXEi2Y6anz9LLWPj83Tnn5fEldnTzU8tO0Ub43wN8AMZBaLaWFuyudVqMIxXCqh7aPD6jO+z5AwtcDa93HUd3fetss+vhub17VXlP6TRt7Kqk/6un/MvVl5P+k8f+ieqP8Aq6f86zVj5BDiXNDb5iRb1W4jwnFJIpR7w6MNfJna+Rw8QGtx3dtrqVoGEue1rbXcQBfzWVWx1NIGZpQ5srnZeXOXZjoCdD1vbzWWmPXNqaeUx1Tnh4YLXeSC06ix6j7lm1NDAxgtRYiyVwOUOAte2n/PRW6nCKtktUycwc6mGsZqMznAM5hy2vezdeytYvT1+FviZVvOaQOLckznZdbOHrffoe5QY9RFT/RrZ4YqnOXNaZXAcu9tR632Wua7x/I/gVKSoeYOS1zhHfNlzG1+9lYjPj+R/AoPpqjH+Q038qz8gWLgZ/xMn8SzKI/5BS/yrPyBYGCaVUnm5B6Bw5dvE1U6xymOMA9916fQuJaF5ngDcuK3JcS6Nrrk33XpGHHwBaiNxHct89woVkVHKBPVO5LmDKXiUxkAnYkEaXUJqqOkgbJNfKXBgsLkkrUVXEXD9bEI5cQbluHsewOBzA6FptuCFZdVnKbnW23p6Sgc4TRyOm5T9C6odIGuHkSRcfas25JJOnkuYpMR4fwipnY2pdC4AAmQuLbWBFvQELZ4Zj2G4nVPpqKqbLOxudzA0ght7X+1XK7ve0wx1OtNoFMKAUhsstriIiyoiIgIiICIiAiIgIiICIiAiIgIiICsVnwN/i/oVfWPW/q2fxf0Ks7Kg3YKpVG7BVXRkIDhZwBHmLqGVudzS1tiAbWU9hdTbEPik3tt0Cm9CAaAbhoB72VVboailxClbU0UjXwuuGvb5Gx+8K5qCQdwnV1e0llm50Lyb9KE29klYf8AV0/516yvJP0pTb2Q1v8AN0351L0sfGvMAIJ1sdlOsqhUNA5Mcdi4+Ab5jf7liFytuf2WGm8fjgdFXh1IznVbGRmVkhaWtawNy21uDYEjra2yYpxE3EaqGWqomSCMOuJJXP8AicCQCdmi1mt2FzutAXXUHOQZdbWNnjDI6eGBgNzkGp7XKxIz4/kfwKtlyRH60eh/AoPqKi/7Apf5WP8AIFg4L/1p9v3lnUn+z9L/ACrPyBYWCW577fvIPQsDe12MPjBGaONgI8tbL0XDj4QvNOHmkcT1pO3Kit969Kw/4QtRG6Y1r2ZXtDh2cLhXBDFoeVHcbeAaKFK0v62A3KhJXU8WLQYcYpjNNG6QPDbsAHc9/wDnqrJb0zllMe10RRklxjjJJv8ACFJscbCSyNjSdy1oF1cczKNNvwUSp2oFNpUApBKq8iIsqIiICIiAiIgIiICIiAiIgIiICIiAsXEHBsTCds39CspYeKODYGE6+MfgVZ2mXSy2piAbeRozba7qbamF8mRkjS/sCsQ0cEzAJWA9ullUYdTgNyBzHN2c06qX7u+o5byZ5I0vtcX+1aT2h1dRR8L1LqUEGQiJ7x+wx2hP9PmtyB4bHXSysYhiVHQU/wDmcjGRPu0F4uHaai3VejivjyY5a3q9Jz4+fFljvW53/HH+yp08TKmnL2SUrmCYBrs3LcTax7EjW3ku8k1k+Wq1tFiuEtnNDh74WzBxvDGzJYgAkkW8xqtgAdSTdx3K39Vy3m5byWa25fRcX2eGcUy3pUryD9Kg29j9b/N03516+tFxxwxQ8Y8LV+BYmXtp6tgHMjtmjcDdrh5ggLz3p635yl6iXr6HxP8ARhxKGR3uvEdFIwnwh8D2m3na65XG/YHxDhcZeK6hnYDYlmcW+0LCvIM3moOcu3qPZnjkBIPJPo4/2WDJwDjbT+riP/qQcpdVhP1g9D+BXRP4Ixtv/h2u9HhXcN4KxSStjbVMFPCTZ0jrkAdTYan0Qe/Uf+z9N/Ks/IFh4IP8Q7+JXajE6RtCKaggq5bMEbSY8gAAt1PkrmBUlRmD5GWc43sg7TAgW8R1ZIOXJEB22K9Hw/4QuJwqnJqzIBvYLuMPbZgutRG2dzzhs4onxsqcrsjpRdod0J8lztLPXVOGRY7JiFJmhhcXZQ7ljLcFtr2s4gEncWFl0dO8stYXvpbusJuN4Iym5OZscRa4mEwOAy7uJbb4dyTtoey78WVk1Md/8+Y83NhMspblr1/v4rMwaaSowxtRLUsqWyjPHI1uXwkDT7brKVijmiqKaJ9K3JTW+rbkLLjpYduyvrll+1dsJrGTewKYUQpgLNbXERFlRERAREQEREBERAREQEREBERAREQFrMflEVLE47c0fgVs1wXtmrp8P4WppqV1nmsY31GR/wDZc+Xk+3hc58Mct1hazxjTWSPztDYWD4idz5KsHEtG59pDlF7AjULxzBa7Fccr42tzRxt6b37rvIXsi93gqKZsTzq240Lu5Xgw+t5s/fUeHHmyeiseHNBGoK1eK18MdQYKnC6qpYG+F7IRI0kgeEeevXTRaLDa99NUl81RM9jjYl7fCF1rJMzQWnQhfT4eacs3PVerDOZxoafF6OlmYI8BrYWjQyCnAy30+d9PtXTjTRWQ9TBXXV+W5qdLt0uoM1+LZYkeI5sUdSGFoZmcwOzeLMGhx8NtrG2/RSY270tzmOt/LNcxrviAPqsaejgmYWviYQd9FluGU6bH7lSyy05es4Sw+Yk+7s17LU1HBGH62gt6ErvrKL2AjWyaHmknBFDfSMj5qw7gekHwhw+xemOgaSommHZNDzRvBsDPhJ+wLNpeFgwjKdPRd77q3spCmA6Joc3Q4SKZttXHe5W1hjyDVbB0bW9Lk7BWp6V0sEjGyGN7mloe3dvmFdIxqutdQMZKaWeoab3EIzObtbTre6wXV1FLTc5+A1b2h/LLTTeIZfFt1bdzrdCb91cZg2KtlaG4/UNgaBpymlzjruTsNvPTUrJfhde6OMNxmobI1ga6QRi7rEkm17C9x06D0Td+Dxl7Y2F43A6aKlp8HxGmhe/KHOpy1jXHe/Yea6Fc2aHFml98eqLXIA5LDp/fzWZhLamjdOazEJq0SEFvMYG5O9rd9PsU9/K9dN01SC4iq4hmpcQmzSOy5jZvSyvt42p42/WtB9DZW4027NERYUREQEREBERAREQEREBERAREQEREBcX7VGNkwXD2PaC01zAbi9vA/VdouX9okc0uDU4pw0vFS0+La2VyxyTyxsY5f0rnMKpqSiyNhZHGT8Otz6rdz0NLVRxNlFyzVpvquBgnq4cbjp5YiOZZrZWt0C6uCilF3e8vbJfQ7rPFl5y4zDcePG79abyOnhYHjKCHm5BGl1kxvDWhrdhssCKRwYA8gutqVdEgC98xk6jtPTYNkCuBy1zZdVdbKni1ts4zdoXE0FZUO4+kvSuDC4tLr+rSLb6AA32+0LpZat1NTSysZzSxpdkvbNYXtdap/FQY6Q/RNW+RpyZowHAkOIsTbTa/zXTilxmWpvc04fUeOVx3lrV306qR4yi+lyqXWLDM+WJj5I3RPc0ExuNy09irgcvN4vXMtsi9h3KTEw08kjYzLI1pcGjdxA2CtB1i030BWJisuIGZlPRNDGStsZshdluSCb3ABA1F97pMd3TOefjjtew2vZWxMMjWtkdctDb2c0W8QuAba9VmWsbLT0DK2hq4qXIyWnNvG2NwDW2NwHEmwBAsDqc3ktu7Vx1KvJjJl+PScWVuP5dqOc1vxEBUJe/Rjcjf3nb/ACCk0AagAFS1Kw6doMYGXtck7k7lSsqgd0e5rGlzyA0bkqbWRSyqAsf32Ho4n0CqKyIjQnXyQY825WHK4hZUrrXWBVPyxuPYIPO+LqnkySvvqSuAlr5JHu8WgF12PHIc9jrb26Ly9tXyaiSOY5Q4WuV1ZfY6Ii4NiIiAiIgIiICIiAiIgIiICIiAiIgLm+PS4YVTZTYGpbm9Mrl0isVsTJYg2RjXAOvYi6s9X2mU3NOAhkBDdBpsslspXTOo4P8AyY/+FW30VO7/ALlvyXf70/jl9utC2VSEvmtrJhdO7YOafIrV4hTtpHNyyg5v2TutY8mN9JcLE2yaq9HJ5rWNkPdXmSLbK5VS4qyo/wACyklgdb9c4tLNNdt7lRjrOIDE53uWHh2XwtM7t79fK2qvMk10KvMlKzZtdq0NRizpoxW09GyKxzujlJdewsQNtTfToto2RYDZNlea/wA1PFds1r9FhYjXYnBPGyho2TwkDPKTcs1N7NuM1gB1G6jVNknpnRwzugeS36xouQAQT9o0+awZKTGXRWixmNsm1zStI/up1etl9zW9MyjxHGZa9jJ8PihpSbGS9yRrrv4emmu9luQVzTKHHGyOf9NRuAHgYaUWB0vfv/dbLCYa6nZMMQrm1Zc68ZEQZkHY23WMvfxprCeM93bagqQKsB3ZTa5Zsb2vgrFxOxo3gq6HLGxR9qQ+oWbFaIvczQFGVD87deqtuu4nKCfRSjjdmBcx2UeSkitrLILXK0+L1DW07hfdXK2eYt+phkI9F5zxrxDV0gMUdHVGw1cIyRdbk9s7YfElc2Z7m3HZcBi9Cya7unVRqcde995w6Mno8EFPfOazfSy2j7DREXBsREQEREBERAREQEREBERAREQEREBWqn4B6oiDGdoFg1cz42OLHWPoiKVY4DinHMShLmxVb2N/3QAsLh2aSeZ8k0jpH5d3G6Ipxf5I1n+ldA0q9EdQiL6LxMmMm6vA7Iiyq8wq806IilE2Eq806oiirrN1caURZWLjFNEWK2k03WLiLQ6NjXajMNERRVlzRHowADyCtlx7oi6xyq25xGxUHeIeIA+oRFpGBX4HheJRObXUFNOLftRhfP8A7UMMpMHqSMMhFO3sxxt9hKIpl01j2+tkRF5HcREQEREBERAREQf/2Q==</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Italian 600kg Sliding Garage Door Motor Kit</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Italian sliding gate motor for up to 600kg, with 2 remotes, SIM module, and app control.</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>3200</v>
+      </c>
+      <c r="D50" t="n">
+        <v>5</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>/9j/4AAQSkZJRgABAQAAAQABAAD/2wBDAAYEBQYFBAYGBQYHBwYIChAKCgkJChQODwwQFxQYGBcUFhYaHSUfGhsjHBYWICwgIyYnKSopGR8tMC0oMCUoKSj/2wBDAQcHBwoIChMKChMoGhYaKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCgoKCj/wAARCADDAV4DASIAAhEBAxEB/8QAHQABAAEFAQEBAAAAAAAAAAAAAAYDBAUHCAECCf/EAEEQAAEDAwMBBAcECQIGAwAAAAABAgMEBREGEiExE0FRYQcUIjJxgZEII6GxFSQzQlJicoLBktEWNEOy4fBjoqP/xAAZAQEBAQEBAQAAAAAAAAAAAAAAAgEDBAX/xAAqEQEAAgIBAwIFBAMAAAAAAAAAAQIDESEEEjFBYQUTUZHwIiMysYGh0f/aAAwDAQACEQMRAD8A6pAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAPh8scfvva34rgsrpKuWxIqoipl2FI5c5IaSRqK1znOTOE7gJQ+5UbOtQxfhz+RQfeqJv8A1HL8GKQ11w/hiT5qUHV0iuXDWpjyyBNVv9GndKv9g/T9H4Tf6CFesyqvVPofbZpF/eUCZtv1EvV0ifFilVaz1li+qStRE43ImVIbHK/vcpmLG9e2flf3TYFzVW+apje1a+rjV6YV0b9rk+C9xZx6eqGe5e7tyip7U+7HnynUz6OwfSSFcsR+LT9yjeit1Fc3In7sitVF/wDqePst/wB69jqSZjcJhHU7H93XPHXqSTtUQ+km8TOWo8y16gjmY91+WSNrMOjWmam538WUXKfBDC1WqJaC7/oq7V01uqFwsdTLE1YZU8UXPHz6E9SVqkX9I1jp71pqpV7USopWOnhk8FRMqnwVEwRkm0Rur09LGO+SKZfE8b+nuyrKaulaxzbk/bjOWNaqO8+UX8DH6gvM9mrtO0KPWaW5VyUznuROGoxz3Lx3rtRDUWkdZXKwKyOF/rFF1WnkXhP6V/d/ImN51BR6iv8AoSoo0karLnIj2PbhWu7B3Gei9e489eprkjjy+n1PwXN0l/3I3Tnn/Ezy2onQBOiA9L4YAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAeOXa1XL0RMgYaqdvrJV7kXanyIldpu2r5VTo1dqfIkckuyGWV3ciuIiqq5VVeq8gFPlE9p3x/wfR8p7zgKidSqwpJ1KjAK7O4y1kd+sqni0xDe4ytlX9cb5tU2PIz+T3IwfW066hmniHp6jT121jFc9yNanVVMnTdDSA+kfUUszX6csTH1VxqE2zpEmVjZ3t+K/ghLKyOuuLVhpJHUNMvDqjH3rk/kRfd/qX5J3lxZLJQWaFYrfTtj3cvevtPkXxc5eVU4ZYteO2OIe7pMmLprRlyR3THiPTf1n/n30gGkvRijEZUahejl6pSxO4/ud3/BPqZXWtFBBqXQMFNG2GGK4vVrI24RMQu7iftQhmuZVj1ZoprU5fXSIq+Cdkpy+VXFXVfb+3e3X5+uzd2ad8W49I4lNU6IAnRAd3ygAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAt692yjlX+XH1Lgsby7FHj+JyIBHLxJ2ducifvKjSOp0Mvf3/dQM8VVTEJnABTxnvO+R7hQi4c7Oe4Co0qNQptenmV4lR+cdwFRiGRs/FdF55/IsWtx73CeZXoqump6uF0s8TUR3Ptc/QQJM+pgjkVkkrUemMpheCzqbzS0qOl7Vs8DffWNMuZ547/ADROUIbdL/WSX2SOSeGlse/dIsE6JNMiNwiZ4VqLjnHPmWNivN5pdU3GrW5Oq7RUJspLb2CNZTImNuHJ1XrnxyO+bb09FsUY9TMxO+ePzy2Ml8tHZRyLdKFrJEyxXTtbu+GVKjLraZ1RW3ChkVvhUMXH4mmbvpOnivNsuFc1I46aSWoVk7WOY5HNVFT+VMr+CGn9IWeSh1TZJLpBA2iZWQ9ssr2KzZuTO7noKTaY/UZaY4tMYrbj7Oz211Gvu1dOvwlb/uVmzQu92WNfg5DkTUtwoKaS1R0dTJE1KCJZG0rIXM35dnOed3TPyPa5XfoPT8lEtRvko3PqHU1LFLuk7aTl+VzuxjjwwU5drsBqovRckN1lGsus9GJvRjWVE71z1diNMIn1/Aw/2f2vdoJk9RvWoWpnY5XptXCPXCbeifAkGpXNbrLS27HLqhEVfFWtOd4jWpXhma33H0n+pStOgCdAU4gAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABjL6v3UKeLs/gZMwmoZ2tqKOFfefuVPPGM/mBF74u6pjb4M/yWCIXt3c1tW9z3I1rWplV4xwRK8XiaaF0dlnpo3Izc6edHezzj2UwqZ+Jdcdr81jabXrXzK+vd7obLDuq5MyqmWQs5e75dyea8ECqda3Wepe+DsYIl91mzcqJ5qvVS1fYaypmkldVwVFQ5cqqucrnr8VQs7Pbn3S509FHK2F0yqm97VciYaq9Mp4GWpan8o0VtFvEsn/xPeX9axW/0san+B+lrlMuX11QueuHqn5Gfh9H6Narprs5ETqrKdE/NykKrbta6SomZTNrqqKJf2jpGR7vPCN/ySpmO0mkT25pHL5vVS/sCYujc9dj/AMiytVbb6+2VzUo5IqyKNJYpO3c5MI5qLwq+CmSsbcXSP+l//aohseWy6migbaIVZBC1ywOyqMRFVceODBWaNVlpdyYxtJXUtzaol/8Aid+RHrLtb6ryvLW4z8Co9Wyy13Ykl6tTMqiZRMp/UhLktUKOcrnyPyiph+12Mr1TKEVrm5vtr8lT/uQm+7kyIJYqWxRPTiRM9++CN3h/L5fiUZNMUL3OVYqZc9EdRwrjp/Lz/wCTN7j1HBi3ttFDbqRtPTsjYxFVcRxtjTlc9GoiEa1ZHG7WekJpUV2yaZrGp/E5nVfJERSWZI5f5ETVGnU4VVkkRM/0mWruOVUtNJ3H5tKE6AJ0AQAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAtblcKO10j6q41MNNTM96WVyNanzU1ZrDWVvu93ghtkiy01Ozc2sjd7EjndzV78InXxUnuu7Yt203U07W73JiRGY97HVPpk5ljgWyXGqpZVp2W2N2+JGZa5mU6KnRfJQJDe7pW3LVkTKmoe+CKRuxnRvu9cd6+ZIHX19RVNqnUVG1YYo2pG2PDXbXIvKeZGdPUNVfbok1vi7bY1sr8OThvTPnypIILFclmmpm0VQsyN5bsXuVO/p+J9PoPl9tu94er79x2rqnvnbPrYloaRi1szZNzWYWLyb5f+SH6XkiotQ0FRUPSOFj3b3r0RFa5CV2+w3N9UzFDUIrF3KrmK1ERPiQdr284VOPMj4hFItEUX0ndqe5s6o1NZOyfH60+RHIqKjInLnPyNVVOnKDtpUpauo9Xeq4R0CI7C+aqVkqoUciLLGi+G5MntZVK211tRC10jYIXuc5iK5G4aq8qnQ+e9aI6RvtxuWo6m3218EVE9zoXyOj3OWNFynfxlUTobQjiktGoqCGSsirIp2StV7Gbdkjcorc9+M8qaAtUlbapo6mFrV3NRznMdhVTz6E80Hday+avt1O58sz1WWZE5dtZjOcfLKgdQSe3ZoXJ3xEbtrfZpsqirtTlCtJqGnZTxUETZJZGM2OVGKqJx5FhQTVTIYttN2aI1OZXIzu8Ov4Fx7tn2SmqTN8tv9v5oSvf4mvrS+uSvpJK6VZHb249naic92eV+hkqy+1G9GOlaxVVURETrgKmEw3niTNVcI5qr4Ipr+a5Tvzulkd5IvUo2+9rRSNqpYXZxsfG56bmbl43Yzju48zJtEcy2mO151Xy2M6THeQfVV1ZHr7RlG1FWaeebC+DUjVV/whWh1XK+pp4paFI+2ax6ffZXY96NaqJjnqir0+Zj/Vl1B6R9L17GLHHbqWpqHIq97ndmn5Kc73i0aq9VOnnHM2yxxqfvqdf7bOToAnQ+e0Z2vZ729pjdtzzjxwU8L6AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAABqvW1FdptVVK0dJNNHsY6HbE5yKqtRHc+7xjoviWlDpujqGTv1ZpuSra5qLK5YNibs9MIvPdz0NvgDSOq7bbpKOki0TapqWVr1SVII3sTbjhM+GS1ksWpqilRkUFaiqxqe05yJ0TPeb17GPOezZn4H0jWp0RPoebJ0tMlptO+X0un+KZunxxjpEaid8w0HTaD1VUTsbK18bc5y6oVMfHkyXpmpLzZ/RDe5Zkpp5XPiylLTbOxj3Ju6JlUzhVVfM3Xg8c1HNVrkRWqmFRe8vD09MEao5db1+brbRbLrj6RpxBoXUlvltkf6V3PqUVW70azp9PA2l6PbtZrpqynsVFHM6nudPPTVbGvTDo+yd1RPBe/uyblk9HmjpKp9Q/TFnWZ67nO9UZyvj0Mra9PWa0ydpa7Tb6OTGN9PTsjdjwyiZOzxOctUfZ6uFDTSN03fUqURMJT1zdivx0RHJxkkH2f8A0fT6cqLpcb/T7LqrW00bVY5Ejj6uxlERVVUTp3J5nQD2te1WvRHNXqiplFKE9Mj2psw1U6J3ARCsp4u3kcqOXLl43KifRCye5sKL2TY4/NGpn6mRuTXx1T41ilV6rlEaxVMbT6cralyr6vLl3CyVD9mU54wnOOehW1xr1WdBUNqK+J0cnaKkrUVUXPOUJHBb7HAsUl0Ri1i7mpvVfHKo3y6GQ0/YI7U508siSTK3HstRrGp5f7kc1frHSlnncldfKVsjU/YQffSZ8MN6fPBm4ZvbNVDLIscjEoWuY9qsdxtRUXr3+Rh6mOzQxujit8LWYTLI8qr8KjkyvxQ1Dqf072al3ss9ukmenCSVsuP/AM2c/VxqbUvpg1FeXOhgnfEx3HZUzeybj+32l+ak6ifRdcl6xqJmHWF8j0NYoGyXS4Mt7nNRyxMrH7+u5PZRVVVRenHHca9ufp10tpeOaLTlFV1sjuklXLsanKrhEXLsZVVxhOpzEsN5uCufK50SOXlXLtz/AJUoutlBTKnr9ar3dVZGv/qmRWsSq2bJeO21pmGzNXfaE1feUfHQ1TbdA7hEpWdnj+5cuX6oTL7INZcbjrjUVZdJqmokfQM+9mVVz954qaBW6UdLxQ0LWqnR8iZU359juqravV9/kqkckfqDNuW4T9p3Fa9nKfDq8ABIAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAF4QFGtp2VdHPTS/s5o3Ru+CphfzAhOq/SxpPTc01PVXBamthVWvp6RnaOavgq+6nzU05qv7TEqK+Kw26npk6JJUu7Z/+luET5qpo30paOvukr9XwV9FVRW5tSsUNSqOSKZVbuTa7oq45MOyzSWm2UVxu9FL2FY3fB2jdu5nOHt/iRcfgo16yqIhKdTeljVeqJXxT1tZO1V/Zo5WR/wChmE+pHEortXM/WZ0hYvKpnb+CFqt8e53ZW+kRmeiYyv0Qeo3Sv/5qRYmpzhzunyQa17N8K/qVoo1/Wal00idWtX/Cf7ni3tkP3dtoWMzj2lTlfkh42htVAmayofI9P3G8Z+Scn1HeYY3dlaqHnxxz+HJnn3a+VhvNw9/exi9Veuxv0Tk9baaKjTNdWoru9rOq/wCSo6nvNfzNJ6vEvVF9n8E5PlbdbqNFWurFkd3tauM/Tk3f5DFL9I0NM/bb6NHvT/qSf+5OgPsgz11Rq+/PrGOZF6gzam3ame0+poJbzS0rdtuo2Nxwjnob2+x1cKiv1nqBZ35a2gZhETCftBr10yXWIACQAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAYnVOnrbqmw1lnvNOk9FVMVj29FTwc1e5ydUUhusfQ/pzU+lLNYKj1mnprS1rKaWFydpsa3G1VVOUXhV8zZAA4Q1N6I9RaKh1NUVNI+WitqRvhuMbcNlY5V6eGP3k7vmaykrK6unbC6V+57kajPdTk/TmaKOeJ0c0bJI3JhzXoioqeCopriq9EVkf6UaHWdI1lPLEyX1mkbGix1Ejmq1Hr4Lhy54548zYnnbduHGU9sokclc6R07eHMXpnyTwD78yJu2gp2xNTx4/BDdXpx9A1ytP6Y1NYpm1lubKszqNrV7SCHHLv5sLnhO7nxIDePRBqG16Rtmp46da201Fv9fqFam1aZOuxyZyvCouU8/ARETzKtoFVXGrqVVJqh6sVeGt4T6FzQ2a519G+qoqCeSmZOymfMxiua2R/utcvcqlw6po66wW61W61yyXhlVNI+dib3TMejdjEanKqio76ndPoH0l/wp6NbVS1lvjo7rPGk1ciJ7TpFzt3/AMyN2p5YK3rwyZc46e+zdqu4Oucdykht8tLURMiWV2Y6mNeXuY5ueiYxlOc9x0h6LfRVZ/R1WXaotU00769zUa6dE3RRonuIqdUzzk2ECdpAAYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAADkRyKjkRUXhUU+JIYpYHQyRsfE5qscxzUVqtVMKip4Y7j7AGD09pHT2nHSOsVlt9vfIqq51PA1jl+aJn5GcAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA//9k=</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
